--- a/data/input/template_pendaftaran.xlsx
+++ b/data/input/template_pendaftaran.xlsx
@@ -1650,17 +1650,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>2026-08-10T12:42:11</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2026-08-10T10:35:19</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:35:19</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>SELESAI (isi=42, lewat=5, tak-berlaku=32)</t>
+          <t>SUDAH SELESAI</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>2026-08-10T12:42:17</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>2026-08-10T10:37:37</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:37:37</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>SELESAI (isi=47, lewat=5, tak-berlaku=29)</t>
+          <t>SUDAH SELESAI</t>
         </is>
       </c>
     </row>
@@ -1950,17 +1950,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>2026-08-10T12:42:23</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2026-08-10T10:39:20</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:39:20</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>SELESAI (isi=40, lewat=5, tak-berlaku=33)</t>
+          <t>SUDAH SELESAI</t>
         </is>
       </c>
     </row>
@@ -2100,17 +2100,17 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>2026-08-10T12:42:29</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2026-08-10T10:41:21</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:41:21</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>SELESAI (isi=44, lewat=5, tak-berlaku=31)</t>
+          <t>SUDAH SELESAI</t>
         </is>
       </c>
     </row>
@@ -2694,17 +2694,17 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>2026-08-10T12:42:36</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>2026-08-10T10:43:39</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:43:39</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>SELESAI (isi=47, lewat=5, tak-berlaku=29)</t>
+          <t>SUDAH SELESAI</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-08-10T10:46:25</t>
+          <t>2026-08-10T12:43:11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>MULAI (isi=43, lewat=10, tak-berlaku=27)</t>
+          <t>GAGAL: TargetClosedError: Locator.count: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:11</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>2026-08-10T10:49:03</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:49:03</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>SELESAI (isi=69, lewat=5, tak-berlaku=25)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3139,17 +3139,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:11</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>2026-08-10T10:51:53</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:51:53</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>SELESAI (isi=1, lewat=12, tak-berlaku=31)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:11</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>2026-08-10T10:55:05</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>2026-08-10T10:55:05</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>SELESAI (isi=69, lewat=6, tak-berlaku=25)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-08-10T10:58:30</t>
+          <t>2026-08-10T12:43:12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>MULAI (isi=42, lewat=7, tak-berlaku=31)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-08-10T11:01:41</t>
+          <t>2026-08-10T12:43:12</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>MULAI (isi=63, lewat=7, tak-berlaku=27)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3951,17 +3951,17 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>2026-08-10T11:04:07</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:04:07</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>SELESAI (isi=53, lewat=5, tak-berlaku=28)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4101,17 +4101,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>2026-08-10T11:06:22</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:06:22</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>SELESAI (isi=47, lewat=5, tak-berlaku=29)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4251,17 +4251,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>2026-08-10T11:08:58</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:08:58</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>SELESAI (isi=65, lewat=5, tak-berlaku=27)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2026-08-10T11:11:46</t>
+          <t>2026-08-10T12:43:12</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>MULAI (isi=31, lewat=7, tak-berlaku=28)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4546,17 +4546,17 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
           <t>2026-08-10T11:13:35</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:13:35</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>SELESAI (isi=42, lewat=5, tak-berlaku=32)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4696,17 +4696,17 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>2026-08-10T11:16:10</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:16:10</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>SELESAI (isi=65, lewat=5, tak-berlaku=27)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4846,17 +4846,17 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>2026-08-10T11:18:19</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:18:19</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>SELESAI (isi=49, lewat=5, tak-berlaku=30)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5107,17 +5107,17 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
           <t>2026-08-10T11:20:36</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:20:36</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>SELESAI (isi=46, lewat=5, tak-berlaku=29)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5257,17 +5257,17 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
           <t>2026-08-10T11:22:45</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:22:45</t>
-        </is>
-      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>SELESAI (isi=49, lewat=5, tak-berlaku=30)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5407,17 +5407,17 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>2026-08-10T11:24:58</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:24:58</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>SELESAI (isi=49, lewat=5, tak-berlaku=30)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5557,17 +5557,17 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
           <t>2026-08-10T11:27:28</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:27:28</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>SELESAI (isi=53, lewat=5, tak-berlaku=28)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>2026-08-10T11:28:53</t>
+          <t>2026-08-10T12:43:12</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>MULAI (isi=33, lewat=0, tak-berlaku=36)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -5852,17 +5852,17 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
           <t>2026-08-10T11:30:37</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:30:37</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>SELESAI (isi=39, lewat=5, tak-berlaku=33)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6002,17 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
           <t>2026-08-10T11:32:23</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:32:23</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>SELESAI (isi=42, lewat=5, tak-berlaku=32)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6152,17 +6152,17 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
           <t>2026-08-10T11:35:32</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:35:32</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>SELESAI (isi=84, lewat=5, tak-berlaku=22)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
           <t>2026-08-10T11:38:11</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:38:11</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>SELESAI (isi=70, lewat=5, tak-berlaku=25)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6452,17 +6452,17 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
           <t>2026-08-10T11:41:10</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:41:10</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>SELESAI (isi=70, lewat=5, tak-berlaku=25)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
           <t>2026-08-10T11:43:02</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:43:02</t>
-        </is>
-      </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>SELESAI (isi=41, lewat=5, tak-berlaku=32)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -6863,17 +6863,17 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
           <t>2026-08-10T11:44:58</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:44:58</t>
-        </is>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>SELESAI (isi=42, lewat=5, tak-berlaku=32)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -7013,17 +7013,17 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
+          <t>2026-08-10T12:43:12</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
           <t>2026-08-10T11:48:39</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>2026-08-10T11:48:39</t>
-        </is>
-      </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>SELESAI (isi=84, lewat=5, tak-berlaku=22)</t>
+          <t>GAGAL: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
